--- a/temp/diversos/Zamac.xlsx
+++ b/temp/diversos/Zamac.xlsx
@@ -339,7 +339,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9574.550544</v>
+        <v>9166.550544</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>

--- a/temp/diversos/Zamac.xlsx
+++ b/temp/diversos/Zamac.xlsx
@@ -339,7 +339,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9166.550544</v>
+        <v>8186.496411</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
